--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_appointments_by_tretspef-Users_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_appointments_by_tretspef-Users_Raw.xlsx
@@ -401,19 +401,19 @@
         <v>1920</v>
       </c>
       <c r="C2">
-        <v>1920</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>1062</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3">
@@ -426,19 +426,19 @@
         <v>2113</v>
       </c>
       <c r="C3">
-        <v>2113</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>2.28</v>
+        <v>1.69</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>1043</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="4">
@@ -451,19 +451,19 @@
         <v>33</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>3.07</v>
+        <v>1.64</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -476,19 +476,19 @@
         <v>831</v>
       </c>
       <c r="C5">
-        <v>831</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>1.36</v>
+        <v>0.91</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>550</v>
+        <v>615</v>
       </c>
     </row>
     <row r="6">
@@ -501,19 +501,19 @@
         <v>64</v>
       </c>
       <c r="C6">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -526,19 +526,19 @@
         <v>144</v>
       </c>
       <c r="C7">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>1.11</v>
+        <v>0.72</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>90</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8">
@@ -551,19 +551,19 @@
         <v>645</v>
       </c>
       <c r="C8">
-        <v>645</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>1.54</v>
+        <v>1.08</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>350</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -576,19 +576,19 @@
         <v>390</v>
       </c>
       <c r="C9">
-        <v>390</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>2.13</v>
+        <v>1.51</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>171</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
-        <v>56683</v>
+        <v>54958</v>
       </c>
       <c r="C10">
-        <v>56683</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>3.44</v>
+        <v>4.43</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="G10">
-        <v>16857</v>
+        <v>14049</v>
       </c>
     </row>
     <row r="11">
@@ -626,19 +626,19 @@
         <v>2505</v>
       </c>
       <c r="C11">
-        <v>2505</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>4.73</v>
+        <v>1.51</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>152</v>
+        <v>25</v>
       </c>
       <c r="G11">
-        <v>1197</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="12">
@@ -651,19 +651,19 @@
         <v>11738</v>
       </c>
       <c r="C12">
-        <v>11738</v>
+        <v>3</v>
       </c>
       <c r="D12">
-        <v>4.07</v>
+        <v>2.69</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G12">
-        <v>3331</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="13">
@@ -676,19 +676,19 @@
         <v>676</v>
       </c>
       <c r="C13">
-        <v>676</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>1.42</v>
+        <v>1.08</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G13">
-        <v>352</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14">
@@ -701,19 +701,19 @@
         <v>336</v>
       </c>
       <c r="C14">
-        <v>336</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>3.89</v>
+        <v>2.16</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>86</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15">
@@ -726,7 +726,7 @@
         <v>3</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -751,19 +751,19 @@
         <v>539</v>
       </c>
       <c r="C16">
-        <v>539</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>258</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17">
@@ -776,19 +776,19 @@
         <v>656</v>
       </c>
       <c r="C17">
-        <v>656</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>2.08</v>
+        <v>1.29</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G17">
-        <v>301</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18">
@@ -801,19 +801,19 @@
         <v>1066</v>
       </c>
       <c r="C18">
-        <v>1066</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>359</v>
+        <v>538</v>
       </c>
     </row>
     <row r="19">
@@ -826,19 +826,19 @@
         <v>48</v>
       </c>
       <c r="C19">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>6.07</v>
+        <v>4.92</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -851,19 +851,19 @@
         <v>53</v>
       </c>
       <c r="C20">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>1.09</v>
+        <v>0.63</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
@@ -876,19 +876,19 @@
         <v>61</v>
       </c>
       <c r="C21">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>1.01</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -901,10 +901,10 @@
         <v>39</v>
       </c>
       <c r="C22">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -913,7 +913,7 @@
         <v>4</v>
       </c>
       <c r="G22">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -926,19 +926,19 @@
         <v>56</v>
       </c>
       <c r="C23">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="D23">
-        <v>15.7</v>
+        <v>4.13</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -951,10 +951,10 @@
         <v>378</v>
       </c>
       <c r="C24">
-        <v>378</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>1.17</v>
+        <v>0.93</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -963,7 +963,7 @@
         <v>11</v>
       </c>
       <c r="G24">
-        <v>269</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25">
@@ -976,10 +976,10 @@
         <v>478</v>
       </c>
       <c r="C25">
-        <v>478</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>0.62</v>
+        <v>0.52</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -988,7 +988,7 @@
         <v>5</v>
       </c>
       <c r="G25">
-        <v>374</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26">
@@ -1001,19 +1001,19 @@
         <v>1208</v>
       </c>
       <c r="C26">
-        <v>1208</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>2.43</v>
+        <v>1.6</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G26">
-        <v>481</v>
+        <v>666</v>
       </c>
     </row>
     <row r="27">
@@ -1026,19 +1026,19 @@
         <v>12</v>
       </c>
       <c r="C27">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>0.63</v>
+        <v>0.3</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -1051,7 +1051,7 @@
         <v>18</v>
       </c>
       <c r="C28">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D28">
         <v>0.5600000000000001</v>
@@ -1098,19 +1098,19 @@
         <v>16</v>
       </c>
       <c r="C30">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G30">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
@@ -1120,22 +1120,22 @@
         </is>
       </c>
       <c r="B31">
-        <v>3137</v>
+        <v>4315</v>
       </c>
       <c r="C31">
-        <v>3137</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>9.01</v>
+        <v>3.12</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="G31">
-        <v>1141</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="32">
@@ -1148,19 +1148,19 @@
         <v>1840</v>
       </c>
       <c r="C32">
-        <v>1840</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>1.74</v>
+        <v>1.14</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G32">
-        <v>957</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="33">
@@ -1173,19 +1173,19 @@
         <v>592</v>
       </c>
       <c r="C33">
-        <v>592</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>1.78</v>
+        <v>1.21</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G33">
-        <v>273</v>
+        <v>358</v>
       </c>
     </row>
     <row r="34">
@@ -1198,19 +1198,19 @@
         <v>1587</v>
       </c>
       <c r="C34">
-        <v>1587</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>4.05</v>
+        <v>1.99</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G34">
-        <v>476</v>
+        <v>755</v>
       </c>
     </row>
     <row r="35">
@@ -1223,19 +1223,19 @@
         <v>756</v>
       </c>
       <c r="C35">
-        <v>756</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>1.1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G35">
-        <v>503</v>
+        <v>543</v>
       </c>
     </row>
     <row r="36">
@@ -1248,19 +1248,19 @@
         <v>17</v>
       </c>
       <c r="C36">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>2.15</v>
+        <v>0.93</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G36">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
@@ -1273,19 +1273,19 @@
         <v>145</v>
       </c>
       <c r="C37">
-        <v>145</v>
+        <v>2</v>
       </c>
       <c r="D37">
-        <v>1.15</v>
+        <v>0.91</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G37">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38">
@@ -1298,19 +1298,19 @@
         <v>919</v>
       </c>
       <c r="C38">
-        <v>919</v>
+        <v>2</v>
       </c>
       <c r="D38">
-        <v>5.24</v>
+        <v>2.31</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G38">
-        <v>265</v>
+        <v>414</v>
       </c>
     </row>
     <row r="39">
@@ -1345,10 +1345,10 @@
         <v>16</v>
       </c>
       <c r="C40">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -1357,7 +1357,7 @@
         <v>5</v>
       </c>
       <c r="G40">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -1370,19 +1370,19 @@
         <v>569</v>
       </c>
       <c r="C41">
-        <v>569</v>
+        <v>2</v>
       </c>
       <c r="D41">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
       <c r="F41">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G41">
-        <v>248</v>
+        <v>321</v>
       </c>
     </row>
     <row r="42">
@@ -1395,7 +1395,7 @@
         <v>10</v>
       </c>
       <c r="C42">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1420,19 +1420,19 @@
         <v>44</v>
       </c>
       <c r="C43">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>1.79</v>
+        <v>0.72</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G43">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44">
@@ -1445,19 +1445,19 @@
         <v>1397</v>
       </c>
       <c r="C44">
-        <v>1397</v>
+        <v>3</v>
       </c>
       <c r="D44">
-        <v>6.3</v>
+        <v>3.49</v>
       </c>
       <c r="E44">
         <v>1</v>
       </c>
       <c r="F44">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="G44">
-        <v>317</v>
+        <v>505</v>
       </c>
     </row>
     <row r="45">
@@ -1470,19 +1470,19 @@
         <v>210</v>
       </c>
       <c r="C45">
-        <v>210</v>
+        <v>3</v>
       </c>
       <c r="D45">
-        <v>12.62</v>
+        <v>2.96</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
       <c r="F45">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="G45">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46">
@@ -1495,10 +1495,10 @@
         <v>37</v>
       </c>
       <c r="C46">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D46">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -1507,7 +1507,7 @@
         <v>7</v>
       </c>
       <c r="G46">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
@@ -1520,19 +1520,19 @@
         <v>83</v>
       </c>
       <c r="C47">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="D47">
-        <v>12.94</v>
+        <v>3.44</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="G47">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B48">
-        <v>1791</v>
+        <v>2217</v>
       </c>
       <c r="C48">
-        <v>1791</v>
+        <v>4</v>
       </c>
       <c r="D48">
-        <v>20.91</v>
+        <v>4.93</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48">
-        <v>121</v>
+        <v>38</v>
       </c>
       <c r="G48">
-        <v>136</v>
+        <v>518</v>
       </c>
     </row>
     <row r="49">
@@ -1570,19 +1570,19 @@
         <v>4301</v>
       </c>
       <c r="C49">
-        <v>4301</v>
+        <v>2</v>
       </c>
       <c r="D49">
-        <v>2.04</v>
+        <v>1.36</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
       <c r="F49">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G49">
-        <v>2020</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="50">
@@ -1595,7 +1595,7 @@
         <v>10</v>
       </c>
       <c r="C50">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>0.79</v>
@@ -1620,19 +1620,19 @@
         <v>34</v>
       </c>
       <c r="C51">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D51">
-        <v>2.63</v>
+        <v>0.96</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
       <c r="F51">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
@@ -1645,19 +1645,19 @@
         <v>2957</v>
       </c>
       <c r="C52">
-        <v>2957</v>
+        <v>4</v>
       </c>
       <c r="D52">
-        <v>11.64</v>
+        <v>4</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="G52">
-        <v>299</v>
+        <v>784</v>
       </c>
     </row>
     <row r="53">
@@ -1692,10 +1692,10 @@
         <v>104</v>
       </c>
       <c r="C54">
-        <v>104</v>
+        <v>5</v>
       </c>
       <c r="D54">
-        <v>7.88</v>
+        <v>5.97</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -1704,7 +1704,7 @@
         <v>25</v>
       </c>
       <c r="G54">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
@@ -1717,10 +1717,10 @@
         <v>79</v>
       </c>
       <c r="C55">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -1729,7 +1729,7 @@
         <v>6</v>
       </c>
       <c r="G55">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56">
@@ -1742,19 +1742,19 @@
         <v>142</v>
       </c>
       <c r="C56">
-        <v>142</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>0.51</v>
+        <v>0.36</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="F56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G56">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57">
@@ -1767,19 +1767,19 @@
         <v>2846</v>
       </c>
       <c r="C57">
-        <v>2846</v>
+        <v>2</v>
       </c>
       <c r="D57">
-        <v>4.19</v>
+        <v>1.87</v>
       </c>
       <c r="E57">
         <v>1</v>
       </c>
       <c r="F57">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="G57">
-        <v>1116</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="58">
@@ -1792,19 +1792,19 @@
         <v>6</v>
       </c>
       <c r="C58">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D58">
-        <v>2.83</v>
+        <v>1.73</v>
       </c>
       <c r="E58">
         <v>1</v>
       </c>
       <c r="F58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1817,19 +1817,19 @@
         <v>2529</v>
       </c>
       <c r="C59">
-        <v>2529</v>
+        <v>2</v>
       </c>
       <c r="D59">
-        <v>4.07</v>
+        <v>2.26</v>
       </c>
       <c r="E59">
         <v>1</v>
       </c>
       <c r="F59">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="G59">
-        <v>868</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="60">
@@ -1842,19 +1842,19 @@
         <v>220</v>
       </c>
       <c r="C60">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="D60">
-        <v>1.51</v>
+        <v>1.1</v>
       </c>
       <c r="E60">
         <v>1</v>
       </c>
       <c r="F60">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G60">
-        <v>123</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61">
@@ -1867,7 +1867,7 @@
         <v>10</v>
       </c>
       <c r="C61">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D61">
         <v>1.21</v>
@@ -1892,7 +1892,7 @@
         <v>4</v>
       </c>
       <c r="C62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D62">
         <v>1.41</v>
@@ -1917,19 +1917,19 @@
         <v>4</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>1.41</v>
+        <v>0.58</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -1942,19 +1942,19 @@
         <v>58</v>
       </c>
       <c r="C64">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="D64">
-        <v>2.1</v>
+        <v>1.28</v>
       </c>
       <c r="E64">
         <v>1</v>
       </c>
       <c r="F64">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G64">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65">
@@ -1967,7 +1967,7 @@
         <v>3</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -1992,19 +1992,19 @@
         <v>10</v>
       </c>
       <c r="C66">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D66">
-        <v>1.22</v>
+        <v>0.82</v>
       </c>
       <c r="E66">
         <v>1</v>
       </c>
       <c r="F66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G66">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
@@ -2017,19 +2017,19 @@
         <v>955</v>
       </c>
       <c r="C67">
-        <v>955</v>
+        <v>2</v>
       </c>
       <c r="D67">
-        <v>3.85</v>
+        <v>2.1</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G67">
-        <v>265</v>
+        <v>436</v>
       </c>
     </row>
     <row r="68">
@@ -2042,19 +2042,19 @@
         <v>388</v>
       </c>
       <c r="C68">
-        <v>388</v>
+        <v>3</v>
       </c>
       <c r="D68">
-        <v>9.99</v>
+        <v>3.49</v>
       </c>
       <c r="E68">
         <v>1</v>
       </c>
       <c r="F68">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="G68">
-        <v>73</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69">
@@ -2067,19 +2067,19 @@
         <v>54</v>
       </c>
       <c r="C69">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="D69">
-        <v>1.48</v>
+        <v>1.03</v>
       </c>
       <c r="E69">
         <v>1</v>
       </c>
       <c r="F69">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G69">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70">
@@ -2092,19 +2092,19 @@
         <v>1718</v>
       </c>
       <c r="C70">
-        <v>1718</v>
+        <v>2</v>
       </c>
       <c r="D70">
-        <v>2.29</v>
+        <v>1.42</v>
       </c>
       <c r="E70">
         <v>1</v>
       </c>
       <c r="F70">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G70">
-        <v>765</v>
+        <v>991</v>
       </c>
     </row>
     <row r="71">
@@ -2117,19 +2117,19 @@
         <v>260</v>
       </c>
       <c r="C71">
-        <v>260</v>
+        <v>1</v>
       </c>
       <c r="D71">
-        <v>0.51</v>
+        <v>0.37</v>
       </c>
       <c r="E71">
         <v>1</v>
       </c>
       <c r="F71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G71">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72">
@@ -2142,19 +2142,19 @@
         <v>5218</v>
       </c>
       <c r="C72">
-        <v>5218</v>
+        <v>2</v>
       </c>
       <c r="D72">
-        <v>2.84</v>
+        <v>1.73</v>
       </c>
       <c r="E72">
         <v>1</v>
       </c>
       <c r="F72">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G72">
-        <v>2193</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="73">
@@ -2167,7 +2167,7 @@
         <v>2</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2192,19 +2192,19 @@
         <v>3317</v>
       </c>
       <c r="C74">
-        <v>3317</v>
+        <v>2</v>
       </c>
       <c r="D74">
-        <v>4.32</v>
+        <v>2.01</v>
       </c>
       <c r="E74">
         <v>1</v>
       </c>
       <c r="F74">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="G74">
-        <v>1374</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="75">
@@ -2217,19 +2217,19 @@
         <v>131</v>
       </c>
       <c r="C75">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="D75">
-        <v>2.12</v>
+        <v>1.2</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
       <c r="F75">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G75">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76">
@@ -2242,19 +2242,19 @@
         <v>128</v>
       </c>
       <c r="C76">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="D76">
-        <v>3.79</v>
+        <v>2.96</v>
       </c>
       <c r="E76">
         <v>1</v>
       </c>
       <c r="F76">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G76">
-        <v>58</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77">
@@ -2267,7 +2267,7 @@
         <v>6</v>
       </c>
       <c r="C77">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D77">
         <v>0.45</v>
@@ -2292,19 +2292,19 @@
         <v>2008</v>
       </c>
       <c r="C78">
-        <v>2008</v>
+        <v>2</v>
       </c>
       <c r="D78">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="E78">
         <v>1</v>
       </c>
       <c r="F78">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G78">
-        <v>904</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="79">
@@ -2317,19 +2317,19 @@
         <v>203</v>
       </c>
       <c r="C79">
-        <v>203</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="F79">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G79">
-        <v>117</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80">
@@ -2342,19 +2342,19 @@
         <v>26819</v>
       </c>
       <c r="C80">
-        <v>26819</v>
+        <v>3</v>
       </c>
       <c r="D80">
-        <v>5.08</v>
+        <v>3.42</v>
       </c>
       <c r="E80">
         <v>1</v>
       </c>
       <c r="F80">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="G80">
-        <v>5425</v>
+        <v>7937</v>
       </c>
     </row>
     <row r="81">
@@ -2367,19 +2367,19 @@
         <v>2770</v>
       </c>
       <c r="C81">
-        <v>2770</v>
+        <v>3</v>
       </c>
       <c r="D81">
-        <v>6.8</v>
+        <v>3.16</v>
       </c>
       <c r="E81">
         <v>1</v>
       </c>
       <c r="F81">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="G81">
-        <v>621</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="82">
@@ -2392,19 +2392,19 @@
         <v>215</v>
       </c>
       <c r="C82">
-        <v>215</v>
+        <v>2</v>
       </c>
       <c r="D82">
-        <v>2.66</v>
+        <v>1.24</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
       <c r="F82">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G82">
-        <v>88</v>
+        <v>128</v>
       </c>
     </row>
     <row r="83">
@@ -2417,19 +2417,19 @@
         <v>1501</v>
       </c>
       <c r="C83">
-        <v>1501</v>
+        <v>2</v>
       </c>
       <c r="D83">
-        <v>4.53</v>
+        <v>2.25</v>
       </c>
       <c r="E83">
         <v>1</v>
       </c>
       <c r="F83">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G83">
-        <v>372</v>
+        <v>636</v>
       </c>
     </row>
     <row r="84">
@@ -2442,19 +2442,19 @@
         <v>596</v>
       </c>
       <c r="C84">
-        <v>596</v>
+        <v>2</v>
       </c>
       <c r="D84">
-        <v>3.47</v>
+        <v>1.87</v>
       </c>
       <c r="E84">
         <v>1</v>
       </c>
       <c r="F84">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G84">
-        <v>226</v>
+        <v>310</v>
       </c>
     </row>
     <row r="85">
@@ -2467,19 +2467,19 @@
         <v>326</v>
       </c>
       <c r="C85">
-        <v>326</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>1.31</v>
+        <v>0.97</v>
       </c>
       <c r="E85">
         <v>1</v>
       </c>
       <c r="F85">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G85">
-        <v>178</v>
+        <v>223</v>
       </c>
     </row>
     <row r="86">
@@ -2492,19 +2492,19 @@
         <v>97</v>
       </c>
       <c r="C86">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="D86">
-        <v>7.69</v>
+        <v>2.45</v>
       </c>
       <c r="E86">
         <v>1</v>
       </c>
       <c r="F86">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G86">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87">
@@ -2517,7 +2517,7 @@
         <v>6</v>
       </c>
       <c r="C87">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D87">
         <v>0.58</v>
@@ -2542,19 +2542,19 @@
         <v>485</v>
       </c>
       <c r="C88">
-        <v>485</v>
+        <v>2</v>
       </c>
       <c r="D88">
-        <v>1.49</v>
+        <v>1.08</v>
       </c>
       <c r="E88">
         <v>1</v>
       </c>
       <c r="F88">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G88">
-        <v>255</v>
+        <v>309</v>
       </c>
     </row>
     <row r="89">
@@ -2567,10 +2567,10 @@
         <v>57</v>
       </c>
       <c r="C89">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="D89">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="E89">
         <v>1</v>
@@ -2579,7 +2579,7 @@
         <v>4</v>
       </c>
       <c r="G89">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90">
@@ -2592,19 +2592,19 @@
         <v>44</v>
       </c>
       <c r="C90">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="D90">
-        <v>2.37</v>
+        <v>1.15</v>
       </c>
       <c r="E90">
         <v>1</v>
       </c>
       <c r="F90">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G90">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91">
@@ -2617,19 +2617,19 @@
         <v>338</v>
       </c>
       <c r="C91">
-        <v>338</v>
+        <v>3</v>
       </c>
       <c r="D91">
-        <v>14</v>
+        <v>3.84</v>
       </c>
       <c r="E91">
         <v>1</v>
       </c>
       <c r="F91">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="G91">
-        <v>41</v>
+        <v>98</v>
       </c>
     </row>
     <row r="92">
@@ -2642,19 +2642,19 @@
         <v>1039</v>
       </c>
       <c r="C92">
-        <v>1039</v>
+        <v>3</v>
       </c>
       <c r="D92">
-        <v>11.86</v>
+        <v>3.4</v>
       </c>
       <c r="E92">
         <v>1</v>
       </c>
       <c r="F92">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="G92">
-        <v>195</v>
+        <v>324</v>
       </c>
     </row>
     <row r="93">
@@ -2689,7 +2689,7 @@
         <v>6</v>
       </c>
       <c r="C94">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D94">
         <v>1.73</v>
@@ -2714,19 +2714,19 @@
         <v>1439</v>
       </c>
       <c r="C95">
-        <v>1439</v>
+        <v>2</v>
       </c>
       <c r="D95">
-        <v>5.49</v>
+        <v>2.61</v>
       </c>
       <c r="E95">
         <v>1</v>
       </c>
       <c r="F95">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="G95">
-        <v>473</v>
+        <v>638</v>
       </c>
     </row>
     <row r="96">
@@ -2739,19 +2739,19 @@
         <v>94</v>
       </c>
       <c r="C96">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="D96">
-        <v>3.25</v>
+        <v>1.98</v>
       </c>
       <c r="E96">
         <v>1</v>
       </c>
       <c r="F96">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G96">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97">
@@ -2764,19 +2764,19 @@
         <v>567</v>
       </c>
       <c r="C97">
-        <v>567</v>
+        <v>3</v>
       </c>
       <c r="D97">
-        <v>6.53</v>
+        <v>3.1</v>
       </c>
       <c r="E97">
         <v>1</v>
       </c>
       <c r="F97">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G97">
-        <v>132</v>
+        <v>217</v>
       </c>
     </row>
     <row r="98">
@@ -2789,10 +2789,10 @@
         <v>185</v>
       </c>
       <c r="C98">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="D98">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2801,7 +2801,7 @@
         <v>4</v>
       </c>
       <c r="G98">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99">
@@ -2811,22 +2811,22 @@
         </is>
       </c>
       <c r="B99">
-        <v>5771</v>
+        <v>5892</v>
       </c>
       <c r="C99">
-        <v>5771</v>
+        <v>2</v>
       </c>
       <c r="D99">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="E99">
         <v>1</v>
       </c>
       <c r="F99">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G99">
-        <v>2973</v>
+        <v>3166</v>
       </c>
     </row>
     <row r="100">
@@ -2839,19 +2839,19 @@
         <v>93</v>
       </c>
       <c r="C100">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="D100">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="E100">
         <v>1</v>
       </c>
       <c r="F100">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G100">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101">
@@ -2864,19 +2864,19 @@
         <v>1885</v>
       </c>
       <c r="C101">
-        <v>1885</v>
+        <v>2</v>
       </c>
       <c r="D101">
-        <v>1.81</v>
+        <v>1.33</v>
       </c>
       <c r="E101">
         <v>1</v>
       </c>
       <c r="F101">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G101">
-        <v>786</v>
+        <v>991</v>
       </c>
     </row>
   </sheetData>
